--- a/data/season_26_27.xlsx
+++ b/data/season_26_27.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukec\OneDrive\Documents\Rprojects\misc_projects\fpl_r\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD4C2B8-EECB-406C-A260-67586EA03735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1616D-5A9A-445B-906A-4E10FD1075AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" activeTab="3" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" activeTab="10" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="season" sheetId="2" r:id="rId1"/>
     <sheet name="transfers" sheetId="10" r:id="rId2"/>
-    <sheet name="week_1_teams" sheetId="11" r:id="rId3"/>
-    <sheet name="luke" sheetId="1" r:id="rId4"/>
-    <sheet name="jamesc" sheetId="3" r:id="rId5"/>
-    <sheet name="jameslm" sheetId="4" r:id="rId6"/>
-    <sheet name="fred" sheetId="5" r:id="rId7"/>
-    <sheet name="amy" sheetId="6" r:id="rId8"/>
-    <sheet name="andy" sheetId="7" r:id="rId9"/>
-    <sheet name="lewis" sheetId="8" r:id="rId10"/>
-    <sheet name="tim" sheetId="9" r:id="rId11"/>
+    <sheet name="luke" sheetId="1" r:id="rId3"/>
+    <sheet name="jamesc" sheetId="3" r:id="rId4"/>
+    <sheet name="jameslm" sheetId="4" r:id="rId5"/>
+    <sheet name="fred" sheetId="5" r:id="rId6"/>
+    <sheet name="amy" sheetId="6" r:id="rId7"/>
+    <sheet name="andy" sheetId="7" r:id="rId8"/>
+    <sheet name="lewis" sheetId="8" r:id="rId9"/>
+    <sheet name="tim" sheetId="9" r:id="rId10"/>
+    <sheet name="week_1_teams" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="119">
   <si>
     <t>gameweek_id</t>
   </si>
@@ -104,6 +104,294 @@
   </si>
   <si>
     <t>points_in</t>
+  </si>
+  <si>
+    <t>Rutter Woke Nonsense (Luke Chapman)</t>
+  </si>
+  <si>
+    <t>BB1</t>
+  </si>
+  <si>
+    <t>Kobbie-Wan Kenobi (Lewis Foster)</t>
+  </si>
+  <si>
+    <t>Sausage Röhl FC (Freddie Lodge)</t>
+  </si>
+  <si>
+    <t>Ivory Toast (Tim Grimes)</t>
+  </si>
+  <si>
+    <t>Jacquet potatoes (Andrew Wignall)</t>
+  </si>
+  <si>
+    <t>Sesko's Finest (Amy Fitzgerald)</t>
+  </si>
+  <si>
+    <t>Daylight Brobbey (James Lee-McHugh)</t>
+  </si>
+  <si>
+    <t>Spence&amp;Spencibility (James Calver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbruggen </t>
+  </si>
+  <si>
+    <t>AVL (H)</t>
+  </si>
+  <si>
+    <t>Done (90) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calafiori </t>
+  </si>
+  <si>
+    <t>COV (H)</t>
+  </si>
+  <si>
+    <t>Done (80) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N.Williams </t>
+  </si>
+  <si>
+    <t>LEE (H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maguire </t>
+  </si>
+  <si>
+    <t>HUL (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frimpong </t>
+  </si>
+  <si>
+    <t>NEW (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.Fernandes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarr lens error </t>
+  </si>
+  <si>
+    <t>EVE (A)</t>
+  </si>
+  <si>
+    <t>Did not play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mbeumo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haaland </t>
+  </si>
+  <si>
+    <t>BOU (H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Pedro </t>
+  </si>
+  <si>
+    <t>FUL (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calvert-Lewin </t>
+  </si>
+  <si>
+    <t>NFO (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinsky </t>
+  </si>
+  <si>
+    <t>BRE (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gomez </t>
+  </si>
+  <si>
+    <t>Done (85) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Sangaré </t>
+  </si>
+  <si>
+    <t>TOT (H)</t>
+  </si>
+  <si>
+    <t>Done (75) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Shea </t>
+  </si>
+  <si>
+    <t>SUN (H)</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lammens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaw </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosquera </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van Hecke </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tzolis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anderson lens error </t>
+  </si>
+  <si>
+    <t>Done (62) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brobbey </t>
+  </si>
+  <si>
+    <t>IPS (A)</t>
+  </si>
+  <si>
+    <t>Done (66) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">van Ewijk </t>
+  </si>
+  <si>
+    <t>ARS (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semenyo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szoboszlai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndiaye </t>
+  </si>
+  <si>
+    <t>CRY (H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groß </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hume </t>
+  </si>
+  <si>
+    <t>Done (79) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virgil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dubravka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röhl </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xhaka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gibbs-White lens error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalot </t>
+  </si>
+  <si>
+    <t>Done (10) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampadu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.Le Fée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isak </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hincapie </t>
+  </si>
+  <si>
+    <t>Done (9) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guéhi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Igor Jesus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hughes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacquet </t>
+  </si>
+  <si>
+    <t>Done (69) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">White </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buendía </t>
+  </si>
+  <si>
+    <t>BHA (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiago </t>
+  </si>
+  <si>
+    <t>Done (82) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roefs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keane </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awoniyi </t>
+  </si>
+  <si>
+    <t>Done (20) (P)</t>
   </si>
 </sst>
 </file>
@@ -197,6 +485,9 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
@@ -213,9 +504,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -237,8 +525,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:J2" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J9" totalsRowShown="0">
+  <autoFilter ref="A1:J9" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3DFDA157-BD05-4F91-BBC2-46C272CA2753}" name="date"/>
     <tableColumn id="2" xr3:uid="{E77E158C-7AE3-4435-9E81-D58EA8264AE1}" name="gameweek_id"/>
@@ -246,7 +534,7 @@
     <tableColumn id="4" xr3:uid="{1A5CC8A7-E0BF-4423-9565-863589D0157E}" name="team"/>
     <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="10"/>
     <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value"/>
+    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{873B883E-CCA1-4415-9B58-AC7C5BD906B9}" name="gw_net"/>
     <tableColumn id="9" xr3:uid="{C348C7FD-EAB4-47B7-9C3E-0CF639A77318}" name="total"/>
     <tableColumn id="10" xr3:uid="{29219B07-DFC0-4696-B9A2-8E2F83EBFA88}" name="chip"/>
@@ -256,25 +544,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
-    <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
-    <tableColumn id="3" xr3:uid="{F960ADAB-11EB-41C7-B173-BB90C61D96DB}" name="player"/>
-    <tableColumn id="4" xr3:uid="{CB96EE6B-0249-4B4F-B07B-1B7820079119}" name="opposition"/>
-    <tableColumn id="5" xr3:uid="{36E531D7-8452-43DE-BFAC-381C118D59BB}" name="status"/>
-    <tableColumn id="6" xr3:uid="{DC0EF4DE-A0D9-4613-B723-C12DAE11622F}" name="points"/>
-    <tableColumn id="7" xr3:uid="{CFEFE364-2359-4EEA-BAEF-E0141AD389DC}" name="importance"/>
-    <tableColumn id="8" xr3:uid="{9EE52753-DED7-4B1C-930C-735773EAAF87}" name="captain"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67AFB369-C03A-462B-972F-AF60CDE2CFAB}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{44789776-FE7D-494A-B94B-2A601E85CB98}" name="player_slot"/>
@@ -309,73 +580,59 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4836A799-F6B3-4BEF-BBC5-B86D809182C4}" name="Table11" displayName="Table11" ref="A1:E2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:E2" xr:uid="{4836A799-F6B3-4BEF-BBC5-B86D809182C4}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{EC775AF2-208C-4E18-A2C0-C09FAF5BC5AC}" name="manager"/>
-    <tableColumn id="2" xr3:uid="{50BD60E3-E646-4E83-8FF3-E85FD0DEF0A4}" name="player_slot"/>
-    <tableColumn id="3" xr3:uid="{0D6D63F1-E523-40C2-8C2D-7CA135E1FB2A}" name="player"/>
-    <tableColumn id="42" xr3:uid="{19A6E6E2-5B4F-4DD6-A6D0-0444B40601FA}" name="captain"/>
-    <tableColumn id="43" xr3:uid="{6974E8D0-3C0E-439E-9495-C19F6F5772B5}" name="total" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
+    <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
+    <tableColumn id="2" xr3:uid="{BE1D58D1-9C51-42D3-AA22-8CAB28CF8604}" name="player"/>
+    <tableColumn id="3" xr3:uid="{BBA3FCC6-806B-41EB-9798-388AD565061B}" name="opposition"/>
+    <tableColumn id="4" xr3:uid="{8A9B9F67-F40D-4762-ABF7-51D6948CCFB8}" name="status"/>
+    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{D89A4728-D353-4540-BF9C-5C72EE4426C5}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
-    <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
-    <tableColumn id="2" xr3:uid="{BE1D58D1-9C51-42D3-AA22-8CAB28CF8604}" name="player"/>
-    <tableColumn id="3" xr3:uid="{BBA3FCC6-806B-41EB-9798-388AD565061B}" name="opposition"/>
-    <tableColumn id="4" xr3:uid="{8A9B9F67-F40D-4762-ABF7-51D6948CCFB8}" name="status"/>
-    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{D89A4728-D353-4540-BF9C-5C72EE4426C5}" name="captain"/>
+    <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
+    <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
+    <tableColumn id="2" xr3:uid="{A4B086A9-1D65-498E-82B0-9E3DDE205578}" name="player"/>
+    <tableColumn id="3" xr3:uid="{EAFCFA61-49CF-4629-92EB-1845A9C161E8}" name="opposition"/>
+    <tableColumn id="4" xr3:uid="{49DB9FCA-5CA9-48A1-8F9F-B6D2EEAFF45A}" name="status"/>
+    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{3D20344A-A9A9-43E1-96DD-6D5E7E4D95B7}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
-    <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
-    <tableColumn id="2" xr3:uid="{A4B086A9-1D65-498E-82B0-9E3DDE205578}" name="player"/>
-    <tableColumn id="3" xr3:uid="{EAFCFA61-49CF-4629-92EB-1845A9C161E8}" name="opposition"/>
-    <tableColumn id="4" xr3:uid="{49DB9FCA-5CA9-48A1-8F9F-B6D2EEAFF45A}" name="status"/>
-    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{3D20344A-A9A9-43E1-96DD-6D5E7E4D95B7}" name="captain"/>
+    <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
+    <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
+    <tableColumn id="2" xr3:uid="{DDB067C6-F23D-40DD-9532-341379943214}" name="player"/>
+    <tableColumn id="3" xr3:uid="{F61B9D23-0C8B-4F9C-9E09-DA9CF7A62D86}" name="opposition"/>
+    <tableColumn id="4" xr3:uid="{F91D60CD-48C9-41AB-B219-B337A638004E}" name="status"/>
+    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{2FE3DCC3-DA4C-4705-A219-64FBCE85BF11}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
-    <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
-    <tableColumn id="2" xr3:uid="{DDB067C6-F23D-40DD-9532-341379943214}" name="player"/>
-    <tableColumn id="3" xr3:uid="{F61B9D23-0C8B-4F9C-9E09-DA9CF7A62D86}" name="opposition"/>
-    <tableColumn id="4" xr3:uid="{F91D60CD-48C9-41AB-B219-B337A638004E}" name="status"/>
-    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{2FE3DCC3-DA4C-4705-A219-64FBCE85BF11}" name="captain"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD2A7E80-7899-44F4-A0E0-E1951D803BBF}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{9A789C6B-DF65-4741-842B-32F8E097183F}" name="player_slot"/>
@@ -390,9 +647,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3EEC9588-A154-4394-B1C6-FB872F361A10}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{CFDBEB1B-AC4B-4140-B9D5-FB0F16BBFA70}" name="player_slot"/>
@@ -407,9 +664,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{25B33829-3E10-4EA1-9ED1-D911F47A3168}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{4C06A930-A949-45AD-BF12-6F05B56443BE}" name="player_slot"/>
@@ -419,6 +676,23 @@
     <tableColumn id="6" xr3:uid="{3B4938B0-8547-4BD6-98DF-2DD13C08936D}" name="points"/>
     <tableColumn id="7" xr3:uid="{E5CBA607-33F5-47AA-A30C-B40057FC3700}" name="importance"/>
     <tableColumn id="8" xr3:uid="{F5F9BF2F-2EE9-4A87-A935-10C972680CF4}" name="captain"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
+    <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
+    <tableColumn id="3" xr3:uid="{F960ADAB-11EB-41C7-B173-BB90C61D96DB}" name="player"/>
+    <tableColumn id="4" xr3:uid="{CB96EE6B-0249-4B4F-B07B-1B7820079119}" name="opposition"/>
+    <tableColumn id="5" xr3:uid="{36E531D7-8452-43DE-BFAC-381C118D59BB}" name="status"/>
+    <tableColumn id="6" xr3:uid="{DC0EF4DE-A0D9-4613-B723-C12DAE11622F}" name="points"/>
+    <tableColumn id="7" xr3:uid="{CFEFE364-2359-4EEA-BAEF-E0141AD389DC}" name="importance"/>
+    <tableColumn id="8" xr3:uid="{9EE52753-DED7-4B1C-930C-735773EAAF87}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -767,14 +1041,249 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="A2" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>933078</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
+        <v>64</v>
+      </c>
+      <c r="I2">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4021058</v>
+      </c>
+      <c r="G3" s="2">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>49</v>
+      </c>
+      <c r="I3">
+        <v>49</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4296597</v>
+      </c>
+      <c r="G4" s="2">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>48</v>
+      </c>
+      <c r="I4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4591122</v>
+      </c>
+      <c r="G5" s="2">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>47</v>
+      </c>
+      <c r="I5">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5683502</v>
+      </c>
+      <c r="G6" s="2">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>43</v>
+      </c>
+      <c r="I6">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>5940242</v>
+      </c>
+      <c r="G7" s="2">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>42</v>
+      </c>
+      <c r="I7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>6192133</v>
+      </c>
+      <c r="G8" s="2">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>41</v>
+      </c>
+      <c r="I8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>6868753</v>
+      </c>
+      <c r="G9" s="2">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>38</v>
+      </c>
+      <c r="I9">
+        <v>38</v>
+      </c>
     </row>
     <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:J2">
+  <conditionalFormatting sqref="A2:J9">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD($B2, 2) = 1</formula>
     </cfRule>
@@ -790,12 +1299,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -824,7 +1330,355 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G2" s="1"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -835,44 +1689,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G2" s="1"/>
-    </row>
-  </sheetData>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88325B3C-A2BA-4A91-9824-FCD22A7EB22B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -918,43 +1739,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87FC1234-A7C8-45C3-8186-14F7B7FDEBAD}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE37CD-4558-41F4-92EA-FE7453319710}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -990,6 +1776,357 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="3">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -999,9 +2136,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A36F238-E413-4105-953D-9BEAF6AEF0DC}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -1035,6 +2172,357 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="3">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="3">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1043,9 +2531,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0779779-8AAD-4A05-B64B-AAE55E86E147}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -1079,6 +2567,357 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="3">
+        <v>9</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="3">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1087,9 +2926,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079AB974-BCF6-45DE-BAD2-52D6AC42558C}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -1126,7 +2965,748 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G2" s="1"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-0.43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1137,12 +3717,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1171,7 +3748,355 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G2" s="1"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1182,9 +4107,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1213,7 +4141,355 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G2" s="1"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/season_26_27.xlsx
+++ b/data/season_26_27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukec\OneDrive\Documents\Rprojects\misc_projects\fpl_r\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1616D-5A9A-445B-906A-4E10FD1075AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9F7A65-F0D3-4A74-BABB-4E4B89488095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" activeTab="10" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="season" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="158">
   <si>
     <t>gameweek_id</t>
   </si>
@@ -392,6 +392,123 @@
   </si>
   <si>
     <t>Done (20) (P)</t>
+  </si>
+  <si>
+    <t>Sarr</t>
+  </si>
+  <si>
+    <t>Tzolis</t>
+  </si>
+  <si>
+    <t>luke</t>
+  </si>
+  <si>
+    <t>Ampadu</t>
+  </si>
+  <si>
+    <t>M.Sangaré</t>
+  </si>
+  <si>
+    <t>andy</t>
+  </si>
+  <si>
+    <t>E.Le Fée</t>
+  </si>
+  <si>
+    <t>tim</t>
+  </si>
+  <si>
+    <t>NEW (H)</t>
+  </si>
+  <si>
+    <t>Done (90)</t>
+  </si>
+  <si>
+    <t>AVL (A)</t>
+  </si>
+  <si>
+    <t>IPS (H)</t>
+  </si>
+  <si>
+    <t>NFO (H)</t>
+  </si>
+  <si>
+    <t>Done (70)</t>
+  </si>
+  <si>
+    <t>Done (45)</t>
+  </si>
+  <si>
+    <t>LEE (A)</t>
+  </si>
+  <si>
+    <t>CRY (A)</t>
+  </si>
+  <si>
+    <t>BHA (H)</t>
+  </si>
+  <si>
+    <t>BRE (H)</t>
+  </si>
+  <si>
+    <t>CHE (A)</t>
+  </si>
+  <si>
+    <t>LIV (A)</t>
+  </si>
+  <si>
+    <t>MUN (A)</t>
+  </si>
+  <si>
+    <t>Done (72)</t>
+  </si>
+  <si>
+    <t>Done (78)</t>
+  </si>
+  <si>
+    <t>HUL (H)</t>
+  </si>
+  <si>
+    <t>FUL (H)</t>
+  </si>
+  <si>
+    <t>Done (63)</t>
+  </si>
+  <si>
+    <t>Done (11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anderson </t>
+  </si>
+  <si>
+    <t>Done (81)</t>
+  </si>
+  <si>
+    <t>Done (77)</t>
+  </si>
+  <si>
+    <t>BOU (A)</t>
+  </si>
+  <si>
+    <t>Done (85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gibbs-White </t>
+  </si>
+  <si>
+    <t>Done (73)</t>
+  </si>
+  <si>
+    <t>Done (89)</t>
+  </si>
+  <si>
+    <t>Done (76)</t>
+  </si>
+  <si>
+    <t>MCI (H)</t>
+  </si>
+  <si>
+    <t>ARS (H)</t>
   </si>
 </sst>
 </file>
@@ -437,7 +554,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -485,7 +602,96 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
@@ -511,6 +717,9 @@
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -525,16 +734,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J9" totalsRowShown="0">
-  <autoFilter ref="A1:J9" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
+  <autoFilter ref="A1:J17" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3DFDA157-BD05-4F91-BBC2-46C272CA2753}" name="date"/>
     <tableColumn id="2" xr3:uid="{E77E158C-7AE3-4435-9E81-D58EA8264AE1}" name="gameweek_id"/>
     <tableColumn id="3" xr3:uid="{4EC2B4AA-BB48-4F1C-AA23-865B4955D775}" name="season_standing"/>
     <tableColumn id="4" xr3:uid="{1A5CC8A7-E0BF-4423-9565-863589D0157E}" name="team"/>
-    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="12"/>
     <tableColumn id="8" xr3:uid="{873B883E-CCA1-4415-9B58-AC7C5BD906B9}" name="gw_net"/>
     <tableColumn id="9" xr3:uid="{C348C7FD-EAB4-47B7-9C3E-0CF639A77318}" name="total"/>
     <tableColumn id="10" xr3:uid="{29219B07-DFC0-4696-B9A2-8E2F83EBFA88}" name="chip"/>
@@ -544,8 +753,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67AFB369-C03A-462B-972F-AF60CDE2CFAB}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{44789776-FE7D-494A-B94B-2A601E85CB98}" name="player_slot"/>
@@ -561,8 +770,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:G2" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G4" totalsRowShown="0">
+  <autoFilter ref="A1:G4" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -580,16 +789,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{BE1D58D1-9C51-42D3-AA22-8CAB28CF8604}" name="player"/>
     <tableColumn id="3" xr3:uid="{BBA3FCC6-806B-41EB-9798-388AD565061B}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{8A9B9F67-F40D-4762-ABF7-51D6948CCFB8}" name="status"/>
-    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{D89A4728-D353-4540-BF9C-5C72EE4426C5}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -597,16 +806,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{A4B086A9-1D65-498E-82B0-9E3DDE205578}" name="player"/>
     <tableColumn id="3" xr3:uid="{EAFCFA61-49CF-4629-92EB-1845A9C161E8}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{49DB9FCA-5CA9-48A1-8F9F-B6D2EEAFF45A}" name="status"/>
-    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="8"/>
     <tableColumn id="8" xr3:uid="{3D20344A-A9A9-43E1-96DD-6D5E7E4D95B7}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -614,16 +823,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{DDB067C6-F23D-40DD-9532-341379943214}" name="player"/>
     <tableColumn id="3" xr3:uid="{F61B9D23-0C8B-4F9C-9E09-DA9CF7A62D86}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{F91D60CD-48C9-41AB-B219-B337A638004E}" name="status"/>
-    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="6"/>
     <tableColumn id="8" xr3:uid="{2FE3DCC3-DA4C-4705-A219-64FBCE85BF11}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -631,8 +840,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD2A7E80-7899-44F4-A0E0-E1951D803BBF}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{9A789C6B-DF65-4741-842B-32F8E097183F}" name="player_slot"/>
@@ -648,8 +857,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3EEC9588-A154-4394-B1C6-FB872F361A10}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{CFDBEB1B-AC4B-4140-B9D5-FB0F16BBFA70}" name="player_slot"/>
@@ -665,8 +874,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{25B33829-3E10-4EA1-9ED1-D911F47A3168}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{4C06A930-A949-45AD-BF12-6F05B56443BE}" name="player_slot"/>
@@ -682,8 +891,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
@@ -1281,9 +1490,241 @@
         <v>38</v>
       </c>
     </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>432791</v>
+      </c>
+      <c r="G10" s="2">
+        <v>100.3</v>
+      </c>
+      <c r="H10">
+        <v>108</v>
+      </c>
+      <c r="I10">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2320860</v>
+      </c>
+      <c r="G11" s="2">
+        <v>100.1</v>
+      </c>
+      <c r="H11">
+        <v>105</v>
+      </c>
+      <c r="I11">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2439660</v>
+      </c>
+      <c r="G12" s="2">
+        <v>100.1</v>
+      </c>
+      <c r="H12">
+        <v>105</v>
+      </c>
+      <c r="I12">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2761818</v>
+      </c>
+      <c r="G13" s="2">
+        <v>100.2</v>
+      </c>
+      <c r="H13">
+        <v>101</v>
+      </c>
+      <c r="I13">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3619481</v>
+      </c>
+      <c r="G14" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="H14">
+        <v>88</v>
+      </c>
+      <c r="I14">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4886627</v>
+      </c>
+      <c r="G15" s="2">
+        <v>100.1</v>
+      </c>
+      <c r="H15">
+        <v>90</v>
+      </c>
+      <c r="I15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>5838676</v>
+      </c>
+      <c r="G16" s="2">
+        <v>100.1</v>
+      </c>
+      <c r="H16">
+        <v>73</v>
+      </c>
+      <c r="I16">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>6036188</v>
+      </c>
+      <c r="G17" s="2">
+        <v>100.1</v>
+      </c>
+      <c r="H17">
+        <v>73</v>
+      </c>
+      <c r="I17">
+        <v>120</v>
+      </c>
+    </row>
     <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:J9">
+  <conditionalFormatting sqref="A2:J17">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD($B2, 2) = 1</formula>
     </cfRule>
@@ -1300,7 +1741,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1678,6 +2119,357 @@
       </c>
       <c r="G16" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21">
+        <v>23</v>
+      </c>
+      <c r="G21" s="1">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26">
+        <v>26</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1699,12 +2491,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330229B3-0B25-4B18-9D20-120CB711B0FB}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1728,6 +2521,66 @@
       </c>
       <c r="G1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1740,7 +2593,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE37CD-4558-41F4-92EA-FE7453319710}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -2127,6 +2980,357 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="3">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="3">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="3">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="3">
+        <v>11</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="3">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="3">
+        <v>9</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="3">
+        <v>8</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="3">
+        <v>6</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2138,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A36F238-E413-4105-953D-9BEAF6AEF0DC}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -2521,6 +3725,357 @@
       </c>
       <c r="G16" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="3">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="3">
+        <v>46</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="3">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="3">
+        <v>9</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="3">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1">
+        <v>-0.14000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2533,7 +4088,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0779779-8AAD-4A05-B64B-AAE55E86E147}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -2915,6 +4470,357 @@
         <v>3</v>
       </c>
       <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="3">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20" s="3">
+        <v>8</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="3">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="3">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="3">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="3">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="3">
+        <v>6</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="3">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="3">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2928,7 +4834,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079AB974-BCF6-45DE-BAD2-52D6AC42558C}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -3315,6 +5221,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27">
+        <v>26</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3325,7 +5582,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.28515625" customWidth="1"/>
@@ -3706,6 +5963,357 @@
       </c>
       <c r="G16" s="1">
         <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23">
+        <v>13</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3718,7 +6326,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4095,6 +6703,357 @@
         <v>1</v>
       </c>
       <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22">
+        <v>46</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4108,7 +7067,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
@@ -4489,6 +7448,357 @@
       </c>
       <c r="G16" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
